--- a/src/assets/files/dkVstep/mau-imoport-duthi-tram.xlsx
+++ b/src/assets/files/dkVstep/mau-imoport-duthi-tram.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\project\angular\v14\dangky-vstep\src\assets\files\dkVstep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E8E8784-EBF9-47D2-9386-C95EC03C5D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4ABC0F9-F7DB-4E95-B8D2-0677DCD2D03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t>Địa chỉ email</t>
   </si>
@@ -138,6 +138,15 @@
   </si>
   <si>
     <t>NguyenVanC@gmail.com</t>
+  </si>
+  <si>
+    <t>Giới tính</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>Nữ</t>
   </si>
 </sst>
 </file>
@@ -395,171 +404,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Roboto"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <u/>
-        <color theme="1"/>
-        <name val="Roboto"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="26">
     <dxf>
       <font>
         <b val="0"/>
@@ -576,6 +428,7 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -592,6 +445,163 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <u/>
+        <color theme="1"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -630,6 +640,40 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -901,10 +945,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Câu trả lời biểu mẫu 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="24"/>
-      <tableStyleElement type="headerRow" dxfId="23"/>
-      <tableStyleElement type="firstRowStripe" dxfId="22"/>
-      <tableStyleElement type="secondRowStripe" dxfId="21"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="25"/>
+      <tableStyleElement type="headerRow" dxfId="24"/>
+      <tableStyleElement type="firstRowStripe" dxfId="23"/>
+      <tableStyleElement type="secondRowStripe" dxfId="22"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -919,25 +963,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:Q4" headerRowDxfId="20" totalsRowDxfId="17" headerRowBorderDxfId="19" tableBorderDxfId="18">
-  <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Trình độ đăng ký" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Họ, tên đệm " dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tên" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ngày sinh" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Dân tộc" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Nơi sinh (chỉ ghi tên tỉnh, sau sáp nhập_x000a_ - ví dụ: Thái Nguyên)" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Số CCCD/Hộ chiếu" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Anh CCCD mặt trước" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Anh CCCD mặt sau" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Số điện thoại liên hệ" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Địa chỉ email" dataDxfId="0"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Địa chỉ học tập/công tác/liên hệ" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Vui lòng tải lên ảnh thẻ (dạng ảnh thẻ, nền trắng hoặc xanh, áo có cổ)" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Vui lòng chọn hình thức nộp lệ phí thi" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Ngày nộp lệ phí thi" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vui lòng tải lên minh chứng nộp lệ phí thi tại đây" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:R4" headerRowDxfId="21" totalsRowDxfId="18" headerRowBorderDxfId="20" tableBorderDxfId="19">
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Trình độ đăng ký" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Họ, tên đệm " dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tên" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ngày sinh" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{8BD2DD4A-8DB1-4E46-842E-04C60F0C7E61}" name="Dân tộc" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Giới tính" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Nơi sinh (chỉ ghi tên tỉnh, sau sáp nhập_x000a_ - ví dụ: Thái Nguyên)" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Số CCCD/Hộ chiếu" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Anh CCCD mặt trước" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Anh CCCD mặt sau" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Số điện thoại liên hệ" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Địa chỉ email" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Địa chỉ học tập/công tác/liên hệ" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Vui lòng tải lên ảnh thẻ (dạng ảnh thẻ, nền trắng hoặc xanh, áo có cổ)" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Vui lòng chọn hình thức nộp lệ phí thi" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Ngày nộp lệ phí thi" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vui lòng tải lên minh chứng nộp lệ phí thi tại đây" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="Câu trả lời biểu mẫu 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1144,29 +1189,29 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="56.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="38.140625" customWidth="1"/>
-    <col min="14" max="14" width="41.7109375" customWidth="1"/>
-    <col min="15" max="15" width="28.140625" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" customWidth="1"/>
-    <col min="17" max="17" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="129.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="24" width="18.85546875" customWidth="1"/>
+    <col min="5" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="38.140625" customWidth="1"/>
+    <col min="15" max="15" width="41.7109375" customWidth="1"/>
+    <col min="16" max="16" width="28.140625" customWidth="1"/>
+    <col min="17" max="17" width="19.7109375" customWidth="1"/>
+    <col min="18" max="18" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="129.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>13</v>
       </c>
@@ -1185,41 +1230,44 @@
       <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -1239,30 +1287,33 @@
         <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="16"/>
       <c r="J2" s="16"/>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="16"/>
+      <c r="L2" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="M2" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="N2" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="20"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="4"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="4"/>
     </row>
-    <row r="3" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -1282,30 +1333,33 @@
         <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="1"/>
+      <c r="L3" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="M3" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="N3" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="4"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <v>3</v>
       </c>
@@ -1325,28 +1379,31 @@
         <v>32</v>
       </c>
       <c r="G4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="5"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="5"/>
+      <c r="L4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="25" t="s">
+      <c r="N4" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="N4" s="21"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="8"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
